--- a/results/tables/parte1/resultados_i_AR1_estacionario.xlsx
+++ b/results/tables/parte1/resultados_i_AR1_estacionario.xlsx
@@ -1,107 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udpcl-my.sharepoint.com/personal/roberto_sepulveda_udp_cl/Documents/Escritorio/Roberto/Magister 2025/MBD0011/Tarea Final/results/tables/parte1/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3A052707981D2F05053F0F3642BF99B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4FC64F-C234-4157-850E-CE9A8D7F21B6}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Regresión</t>
-  </si>
-  <si>
-    <t>k estimado</t>
-  </si>
-  <si>
-    <t>p-value usual</t>
-  </si>
-  <si>
-    <t>Significativo usual</t>
-  </si>
-  <si>
-    <t>p-value HAC</t>
-  </si>
-  <si>
-    <t>Significativo HAC</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>Y1 ~ X1</t>
-  </si>
-  <si>
-    <t>Y2 ~ X2</t>
-  </si>
-  <si>
-    <t>Y3 ~ X3</t>
-  </si>
-  <si>
-    <t>Y4 ~ X4</t>
-  </si>
-  <si>
-    <t>Y5 ~ X5</t>
-  </si>
-  <si>
-    <t>Y6 ~ X6</t>
-  </si>
-  <si>
-    <t>Y7 ~ X7</t>
-  </si>
-  <si>
-    <t>Y8 ~ X8</t>
-  </si>
-  <si>
-    <t>Y9 ~ X9</t>
-  </si>
-  <si>
-    <t>Y10 ~ X10</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -120,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -422,270 +408,299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>9.6616794025296091E-2</v>
-      </c>
-      <c r="C2">
-        <v>3.000675174508693E-3</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Regresión</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>k estimado</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>p-value usual</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Significativo usual</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p-value HAC</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Significativo HAC</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Y1 ~ X1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.09661679402529609</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.003000675174508693</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>3.5567374750078651E-2</v>
+      <c r="E2" t="n">
+        <v>0.03556737475007865</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>8.7902639953164607E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>-2.1202408924075291E-2</v>
-      </c>
-      <c r="C3">
-        <v>0.49249661605411549</v>
+      <c r="G2" t="n">
+        <v>0.008790263995316461</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Y2 ~ X2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.02120240892407529</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4924966160541155</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>0.63006396121329722</v>
+      <c r="E3" t="n">
+        <v>0.6300639612132972</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>4.7213625924158448E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>1.583460350309128E-2</v>
-      </c>
-      <c r="C4">
-        <v>0.64447423973860385</v>
+      <c r="G3" t="n">
+        <v>0.0004721362592415845</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Y3 ~ X3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.01583460350309128</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6444742397386038</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>0.73313244042835413</v>
+      <c r="E4" t="n">
+        <v>0.7331324404283541</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>2.1344895926267429E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>6.5124508391519148E-2</v>
-      </c>
-      <c r="C5">
-        <v>4.0296161369066177E-2</v>
+      <c r="G4" t="n">
+        <v>0.0002134489592626743</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Y4 ~ X4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.06512450839151915</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.04029616136906618</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.1148024801169187</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>4.2070349287660616E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>2.8591505175318041E-2</v>
-      </c>
-      <c r="C6">
-        <v>0.37105920138411208</v>
+      <c r="G5" t="n">
+        <v>0.004207034928766062</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Y5 ~ X5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.02859150517531804</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3710592013841121</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>0.51781910548083276</v>
+      <c r="E6" t="n">
+        <v>0.5178191054808328</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>8.0179784785627817E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>3.4857351550120583E-2</v>
-      </c>
-      <c r="C7">
-        <v>0.29962716929244959</v>
+      <c r="G6" t="n">
+        <v>0.0008017978478562782</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Y6 ~ X6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03485735155012058</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2996271692924496</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>0.46135796094833159</v>
+      <c r="E7" t="n">
+        <v>0.4613579609483316</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>1.077967562441162E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>-1.186896927532793E-3</v>
-      </c>
-      <c r="C8">
-        <v>0.96985453011576439</v>
+      <c r="G7" t="n">
+        <v>0.001077967562441162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Y7 ~ X7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.001186896927532793</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9698545301157644</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
-      <c r="E8">
-        <v>0.98082775721902271</v>
+      <c r="E8" t="n">
+        <v>0.9808277572190227</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="G8">
-        <v>1.43171787558849E-6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>5.1122381662540579E-2</v>
-      </c>
-      <c r="C9">
+      <c r="G8" t="n">
+        <v>1.43171787558849e-06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Y8 ~ X8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.05112238166254058</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.1027334543572489</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
-      <c r="E9">
-        <v>0.22038055087719699</v>
+      <c r="E9" t="n">
+        <v>0.220380550877197</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
-      <c r="G9">
-        <v>2.6657012659403461E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>-7.2878496170801471E-2</v>
-      </c>
-      <c r="C10">
-        <v>2.8472642277626019E-2</v>
+      <c r="G9" t="n">
+        <v>0.002665701265940346</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Y9 ~ X9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.07287849617080147</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.02847264227762602</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0.1443766682712071</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
-      <c r="G10">
-        <v>4.7996899831961306E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>-0.10905984678273881</v>
-      </c>
-      <c r="C11">
-        <v>6.7424581585554867E-4</v>
+      <c r="G10" t="n">
+        <v>0.004799689983196131</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Y10 ~ X10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.1090598467827388</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0006742458158555487</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
-      <c r="E11">
-        <v>3.4480854273812871E-3</v>
+      <c r="E11" t="n">
+        <v>0.003448085427381287</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
-      <c r="G11">
-        <v>1.152101332245303E-2</v>
+      <c r="G11" t="n">
+        <v>0.01152101332245303</v>
       </c>
     </row>
   </sheetData>
